--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1998-05-13</t>
+          <t>1998-05-14</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1998-05-08</t>
+          <t>1998-05-09</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1998-05-08</t>
+          <t>1998-05-09</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2000-08-15</t>
+          <t>2000-08-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -3237,7 +3237,7 @@
         <is>
           <t>第3号屋
 2507呎 (4+房)
-(98年-05月-13日)
+(98年-05月-14日)
 $4,706万
 $18,771/呎</t>
         </is>
@@ -3246,7 +3246,7 @@
         <is>
           <t>第5号屋
 2507呎 (4+房)
-(98年-05月-08日)
+(98年-05月-09日)
 $4,600万
 $18,349/呎</t>
         </is>
@@ -3289,7 +3289,7 @@
         <is>
           <t>第9号屋
 2546呎 (4+房)
-(98年-05月-08日)
+(98年-05月-09日)
 $4,880万
 $19,167/呎</t>
         </is>
@@ -3429,7 +3429,7 @@
         <is>
           <t>第25号屋
 3302呎 (4+房)
-(21年-03月-04日)
+(21年-03月-05日)
 $1.25亿
 $37,955/呎</t>
         </is>
@@ -3481,7 +3481,7 @@
         <is>
           <t>第30号屋
 3337呎 (4+房)
-(00年-08月-15日)
+(00年-08月-16日)
 $5,700万
 $17,081/呎</t>
         </is>

--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1129,7 +1129,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>第8号屋</t>
+          <t>第9号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1148,27 +1148,23 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2507</v>
+        <v>2546</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>1998-05-09</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>48800000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>19167</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1195,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>第9号屋</t>
+          <t>第10号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1218,23 +1214,27 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2546</v>
+        <v>2500</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1998-05-09</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>48800000</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>19167</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>第10号屋</t>
+          <t>第11号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2500</v>
+        <v>2476</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>第11号屋</t>
+          <t>第12号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1405,7 +1405,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>第12号屋</t>
+          <t>第13号屋</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>第13号屋</t>
+          <t>第15号屋</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>第15号屋</t>
+          <t>第16号屋</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>第16号屋</t>
+          <t>第17号屋</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>第17号屋</t>
+          <t>第18号屋</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>第18号屋</t>
+          <t>第19号屋</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>第19号屋</t>
+          <t>第20号屋</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2476</v>
+        <v>2500</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>第20号屋</t>
+          <t>第21号屋</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1914,11 +1914,11 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2500</v>
+        <v>3343</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>第21号屋</t>
+          <t>第22号屋</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1984,11 +1984,11 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3343</v>
+        <v>3302</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2028,14 +2028,14 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>第22号屋</t>
+          <t>第23号屋</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>第23号屋</t>
+          <t>第25号屋</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2128,23 +2128,19 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2021-03-05</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>125328000</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>37955</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2153,12 +2149,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2168,14 +2164,14 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>第25号屋</t>
+          <t>第26号屋</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2198,19 +2194,23 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>125328000</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>37955</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>第26号屋</t>
+          <t>第27号屋</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>第27号屋</t>
+          <t>第28号屋</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>第28号屋</t>
+          <t>第29号屋</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>第29号屋</t>
+          <t>第30号屋</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2470,27 +2470,23 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3302</v>
+        <v>3337</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2000-08-16</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>17081</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2499,12 +2495,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2514,14 +2510,14 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>第30号屋</t>
+          <t>第31号屋</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2540,23 +2536,27 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3337</v>
+        <v>3343</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2000-08-16</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>57000000</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>17081</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>第31号屋</t>
+          <t>第32号屋</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3343</v>
+        <v>3302</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>第32号屋</t>
+          <t>第33号屋</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>第33号屋</t>
+          <t>第35号屋</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2797,7 +2797,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>第35号屋</t>
+          <t>第36号屋</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>第36号屋</t>
+          <t>第37号屋</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>第37号屋</t>
+          <t>第38号屋</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3302</v>
+        <v>3337</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2999,76 +2999,6 @@
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>第38号屋</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>3337</v>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3143,7 +3073,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>34 套</t>
+          <t>33 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -3168,7 +3098,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>26 套</t>
+          <t>25 套</t>
         </is>
       </c>
     </row>
@@ -3276,16 +3206,7 @@
           <t>第 2 行</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>第8号屋
-2507呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>第9号屋
 2546呎 (4+房)
@@ -3294,7 +3215,7 @@
 $19,167/呎</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>第10号屋
 2500呎 (4+房)
@@ -3303,7 +3224,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>第11号屋
 2476呎 (4+房)
@@ -3312,7 +3233,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>第12号屋
 2476呎 (4+房)
@@ -3321,7 +3242,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>第13号屋
 2476呎 (4+房)
@@ -3330,14 +3251,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>第 3 行</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>第15号屋
 2476呎 (4+房)
@@ -3346,7 +3260,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>第16号屋
 2476呎 (4+房)
@@ -3355,7 +3276,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>第17号屋
 2476呎 (4+房)
@@ -3364,7 +3285,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>第18号屋
 2476呎 (4+房)
@@ -3373,7 +3294,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>第19号屋
 2476呎 (4+房)
@@ -3382,7 +3303,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>第20号屋
 2500呎 (4+房)
@@ -3391,14 +3312,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>第 4 行</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>第21号屋
 3343呎 (4+房)
@@ -3407,7 +3321,14 @@
 -</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>第22号屋
 3302呎 (4+房)
@@ -3416,7 +3337,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>第23号屋
 3302呎 (4+房)
@@ -3425,7 +3346,7 @@
 -</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>第25号屋
 3302呎 (4+房)
@@ -3434,7 +3355,7 @@
 $37,955/呎</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>第26号屋
 3302呎 (4+房)
@@ -3443,7 +3364,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>第27号屋
 3302呎 (4+房)
@@ -3452,14 +3373,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>第28号屋
 3302呎 (4+房)
@@ -3468,7 +3382,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>第29号屋
 3302呎 (4+房)
@@ -3477,7 +3398,7 @@
 -</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>第30号屋
 3337呎 (4+房)
@@ -3486,7 +3407,7 @@
 $17,081/呎</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>第31号屋
 3343呎 (4+房)
@@ -3495,7 +3416,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>第32号屋
 3302呎 (4+房)
@@ -3504,7 +3425,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>第33号屋
 3302呎 (4+房)
@@ -3513,14 +3434,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>第35号屋
 3302呎 (4+房)
@@ -3529,7 +3443,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>第36号屋
 3302呎 (4+房)
@@ -3538,7 +3459,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>第37号屋
 3302呎 (4+房)
@@ -3547,7 +3468,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>第38号屋
 3337呎 (4+房)
@@ -3556,6 +3477,7 @@
 暂无呎价</t>
         </is>
       </c>
+      <c r="E11" s="19" t="inlineStr"/>
       <c r="F11" s="19" t="inlineStr"/>
       <c r="G11" s="19" t="inlineStr"/>
     </row>

--- a/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1129,7 +1129,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>第9号屋</t>
+          <t>第8号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1148,23 +1148,27 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2546</v>
+        <v>2507</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1998-05-09</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>48800000</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>19167</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1195,7 +1199,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>第10号屋</t>
+          <t>第9号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1214,27 +1218,23 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2500</v>
+        <v>2546</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>1998-05-09</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>48800000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>19167</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>第11号屋</t>
+          <t>第10号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2476</v>
+        <v>2500</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>第12号屋</t>
+          <t>第11号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1405,7 +1405,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>第13号屋</t>
+          <t>第12号屋</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>第15号屋</t>
+          <t>第13号屋</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>第16号屋</t>
+          <t>第15号屋</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>第17号屋</t>
+          <t>第16号屋</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>第18号屋</t>
+          <t>第17号屋</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>第19号屋</t>
+          <t>第18号屋</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>第20号屋</t>
+          <t>第19号屋</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2500</v>
+        <v>2476</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>第21号屋</t>
+          <t>第20号屋</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1914,11 +1914,11 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3343</v>
+        <v>2500</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>第22号屋</t>
+          <t>第21号屋</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1984,11 +1984,11 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3302</v>
+        <v>3343</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2028,14 +2028,14 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>第23号屋</t>
+          <t>第22号屋</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>第25号屋</t>
+          <t>第23号屋</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2128,19 +2128,23 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>125328000</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>37955</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2149,12 +2153,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2164,14 +2168,14 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>第26号屋</t>
+          <t>第25号屋</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2194,23 +2198,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-03-05</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>125328000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>37955</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>第27号屋</t>
+          <t>第26号屋</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>第28号屋</t>
+          <t>第27号屋</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>第29号屋</t>
+          <t>第28号屋</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>第30号屋</t>
+          <t>第29号屋</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2470,23 +2470,27 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3337</v>
+        <v>3302</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2000-08-16</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>57000000</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>17081</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2495,12 +2499,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2510,14 +2514,14 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>第31号屋</t>
+          <t>第30号屋</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2536,27 +2540,23 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3343</v>
+        <v>3337</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2000-08-16</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>17081</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>第32号屋</t>
+          <t>第31号屋</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3302</v>
+        <v>3343</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>第33号屋</t>
+          <t>第32号屋</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>第35号屋</t>
+          <t>第33号屋</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2797,7 +2797,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>第36号屋</t>
+          <t>第35号屋</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>第37号屋</t>
+          <t>第36号屋</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2937,68 +2937,138 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>第37号屋</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>3302</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>第38号屋</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>3337</v>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3073,7 +3143,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>33 套</t>
+          <t>34 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -3098,7 +3168,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>25 套</t>
+          <t>26 套</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3276,16 @@
           <t>第 2 行</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>第8号屋
+2507呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>第9号屋
 2546呎 (4+房)
@@ -3215,7 +3294,7 @@
 $19,167/呎</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>第10号屋
 2500呎 (4+房)
@@ -3224,7 +3303,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>第11号屋
 2476呎 (4+房)
@@ -3233,7 +3312,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>第12号屋
 2476呎 (4+房)
@@ -3242,7 +3321,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>第13号屋
 2476呎 (4+房)
@@ -3251,7 +3330,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>第15号屋
 2476呎 (4+房)
@@ -3260,14 +3346,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>第 3 行</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>第16号屋
 2476呎 (4+房)
@@ -3276,7 +3355,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>第17号屋
 2476呎 (4+房)
@@ -3285,7 +3364,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>第18号屋
 2476呎 (4+房)
@@ -3294,7 +3373,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>第19号屋
 2476呎 (4+房)
@@ -3303,7 +3382,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>第20号屋
 2500呎 (4+房)
@@ -3312,7 +3391,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>第21号屋
 3343呎 (4+房)
@@ -3321,14 +3407,7 @@
 -</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>第 4 行</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>第22号屋
 3302呎 (4+房)
@@ -3337,7 +3416,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>第23号屋
 3302呎 (4+房)
@@ -3346,7 +3425,7 @@
 -</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>第25号屋
 3302呎 (4+房)
@@ -3355,7 +3434,7 @@
 $37,955/呎</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>第26号屋
 3302呎 (4+房)
@@ -3364,7 +3443,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>第27号屋
 3302呎 (4+房)
@@ -3373,7 +3452,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>第28号屋
 3302呎 (4+房)
@@ -3382,14 +3468,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>第29号屋
 3302呎 (4+房)
@@ -3398,7 +3477,7 @@
 -</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>第30号屋
 3337呎 (4+房)
@@ -3407,7 +3486,7 @@
 $17,081/呎</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>第31号屋
 3343呎 (4+房)
@@ -3416,7 +3495,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>第32号屋
 3302呎 (4+房)
@@ -3425,7 +3504,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>第33号屋
 3302呎 (4+房)
@@ -3434,7 +3513,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>第35号屋
 3302呎 (4+房)
@@ -3443,14 +3529,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>第36号屋
 3302呎 (4+房)
@@ -3459,7 +3538,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>第37号屋
 3302呎 (4+房)
@@ -3468,7 +3547,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>第38号屋
 3337呎 (4+房)
@@ -3477,7 +3556,6 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr"/>
       <c r="F11" s="19" t="inlineStr"/>
       <c r="G11" s="19" t="inlineStr"/>
     </row>
